--- a/kafka-auto-matching.xlsx
+++ b/kafka-auto-matching.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vladimir.polyakov\Desktop\KRS-238\IDEA\kafka-auto-matching\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vladimir.polyakov\Desktop\KRS-238\IDEA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B13654E-BC66-4FE4-BD08-F70E62ACA936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F5898E-3DA1-4D50-A350-775A2E431FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="46">
   <si>
     <t>Headers</t>
   </si>
@@ -552,17 +552,398 @@
 	"docSeries": "45"
 }</t>
   </si>
+  <si>
+    <t xml:space="preserve">СНИЛС+ФИ+ДР </t>
+  </si>
+  <si>
+    <t>{
+	"emdrId": "224.16.25.09.000241015",
+	"kind": "224",
+	"organization": "1.2.643.5.1.13.13.12.2.16.1080",
+	"creationDateTime": "2026-06-20T08:25:38.000+00:00",
+	"patientSnils": "33276225363",
+	"regOkato": "92000000000",
+	"regionCode": "16",
+	"signer": [],
+	"processingStatus": "NEW",
+	"supplierId": "emdr-rmis-1",
+	"supplierDocId": "77700268-6023-4779-9902-000840bf1516",
+	"deltaMessageTime": "2025-11-24T08:48:14.000+00:00",
+	"patient": {
+		"surname": "Красильникова",
+		"name": "Ольга",
+		"birthDate": "1980-09-05",
+		"snils": "33276225363",
+		"enp": "",
+		"otherId": {
+			"number": "",
+			"type": "44"
+		}
+	},
+	"representative": {
+		"surname": "",
+		"name": "",
+		"patrName": "",
+		"snils": ""
+	},
+	"docNumber": "0303202301",
+	"docSeries": "45"
+}</t>
+  </si>
+  <si>
+    <t>СНИЛС+ИО+ДР</t>
+  </si>
+  <si>
+    <t>{
+	"emdrId": "224.16.25.09.000241016",
+	"kind": "224",
+	"organization": "1.2.643.5.1.13.13.12.2.16.1080",
+	"creationDateTime": "2026-06-20T08:25:38.000+00:00",
+	"patientSnils": "33276225363",
+	"regOkato": "92000000000",
+	"regionCode": "16",
+	"signer": [],
+	"processingStatus": "NEW",
+	"supplierId": "emdr-rmis-1",
+	"supplierDocId": "77700268-6023-4779-9902-000840bf1516",
+	"deltaMessageTime": "2025-11-24T08:48:14.000+00:00",
+	"patient": {
+		"surname1": "Красильникова",
+		"name": "Ольга",
+		"patrName": "Александровна",
+		"birthDate": "1980-09-05",
+		"snils": "33276225363",
+		"enp1": "1851982082633279",
+		"otherId1": {
+			"number": "8081342910",
+			"type": "1"
+		}
+	},
+	"representative": {
+		"surname": "",
+		"name": "",
+		"patrName": "",
+		"snils": ""
+	},
+	"docNumber": "0303202301",
+	"docSeries": "45"
+}</t>
+  </si>
+  <si>
+    <t>СНИЛС+ДР+ДУЛ</t>
+  </si>
+  <si>
+    <t>{
+	"emdrId": "224.16.25.09.000241017",
+	"kind": "224",
+	"organization": "1.2.643.5.1.13.13.12.2.16.1080",
+	"creationDateTime": "2026-06-20T08:25:38.000+00:00",
+	"patientSnils": "33276225363",
+	"regOkato": "92000000000",
+	"regionCode": "16",
+	"signer": [],
+	"processingStatus": "NEW",
+	"supplierId": "emdr-rmis-1",
+	"supplierDocId": "77700268-6023-4779-9902-000840bf1516",
+	"deltaMessageTime": "2025-11-24T08:48:14.000+00:00",
+	"patient": {
+		"surname1": "Красильникова",
+		"name1": "Ольга",
+		"patrName1": "Александровна",
+		"birthDate": "1980-09-05",
+		"snils": "33276225363",
+		"enp1": "1851982082633279",
+		"otherId": {
+			"number": "8081342910",
+			"type": "1"
+		}
+	},
+	"representative": {
+		"surname": "",
+		"name": "",
+		"patrName": "",
+		"snils": ""
+	},
+	"docNumber": "0303202301",
+	"docSeries": "45"
+}</t>
+  </si>
+  <si>
+    <t>СНИЛС+ФИ+ДУЛ</t>
+  </si>
+  <si>
+    <t>{
+	"emdrId": "224.16.25.09.000241018",
+	"kind": "224",
+	"organization": "1.2.643.5.1.13.13.12.2.16.1080",
+	"creationDateTime": "2026-06-20T08:25:38.000+00:00",
+	"patientSnils": "33276225363",
+	"regOkato": "92000000000",
+	"regionCode": "16",
+	"signer": [],
+	"processingStatus": "NEW",
+	"supplierId": "emdr-rmis-1",
+	"supplierDocId": "77700268-6023-4779-9902-000840bf1516",
+	"deltaMessageTime": "2025-11-24T08:48:14.000+00:00",
+	"patient": {
+		"surname": "Красильникова",
+		"name": "Ольга",
+		"patrName1": "Александровна",
+		"birthDate1": "1980-09-05",
+		"snils": "33276225363",
+		"enp1": "1851982082633279",
+		"otherId": {
+			"number": "8081342910",
+			"type": "1"
+		}
+	},
+	"representative": {
+		"surname": "",
+		"name": "",
+		"patrName": "",
+		"snils": ""
+	},
+	"docNumber": "0303202301",
+	"docSeries": "45"
+}</t>
+  </si>
+  <si>
+    <t>СНИЛС+ИО+ДУЛ</t>
+  </si>
+  <si>
+    <t>{
+	"emdrId": "224.16.25.09.000241019",
+	"kind": "224",
+	"organization": "1.2.643.5.1.13.13.12.2.16.1080",
+	"creationDateTime": "2026-06-20T08:25:38.000+00:00",
+	"patientSnils": "33276225363",
+	"regOkato": "92000000000",
+	"regionCode": "16",
+	"signer": [],
+	"processingStatus": "NEW",
+	"supplierId": "emdr-rmis-1",
+	"supplierDocId": "77700268-6023-4779-9902-000840bf1516",
+	"deltaMessageTime": "2025-11-24T08:48:14.000+00:00",
+	"patient": {
+		"surname1": "Красильникова",
+		"name": "Ольга",
+		"patrName": "Александровна",
+		"birthDate1": "1980-09-05",
+		"snils": "33276225363",
+		"enp1": "1851982082633279",
+		"otherId": {
+			"number": "8081342910",
+			"type": "1"
+		}
+	},
+	"representative": {
+		"surname": "",
+		"name": "",
+		"patrName": "",
+		"snils": ""
+	},
+	"docNumber": "0303202301",
+	"docSeries": "45"
+}</t>
+  </si>
+  <si>
+    <t>{
+	"emdrId": "224.16.25.09.000241020",
+	"kind": "224",
+	"organization": "1.2.643.5.1.13.13.12.2.16.1080",
+	"creationDateTime": "2026-06-20T08:25:38.000+00:00",
+	"patientSnils": "33276225363",
+	"regOkato": "92000000000",
+	"regionCode": "16",
+	"signer": [],
+	"processingStatus": "NEW",
+	"supplierId": "emdr-rmis-1",
+	"supplierDocId": "77700268-6023-4779-9902-000840bf1516",
+	"deltaMessageTime": "2025-11-24T08:48:14.000+00:00",
+	"patient": {
+		"surname": "Красильникова",
+		"name": "Ольга",
+		"birthDate": "1980-09-05",
+		"snils": "33276225363",
+		"enp": "",
+		"otherId": {
+			"number": "",
+			"type": "44"
+		}
+	},
+	"representative": {
+		"surname": "",
+		"name": "",
+		"patrName": "",
+		"snils": ""
+	},
+	"docNumber": "0303202301",
+	"docSeries": "45"
+}</t>
+  </si>
+  <si>
+    <t>{
+	"emdrId": "224.16.25.09.000241021",
+	"kind": "224",
+	"organization": "1.2.643.5.1.13.13.12.2.16.1080",
+	"creationDateTime": "2026-06-20T08:25:38.000+00:00",
+	"patientSnils": "33276225363",
+	"regOkato": "92000000000",
+	"regionCode": "16",
+	"signer": [],
+	"processingStatus": "NEW",
+	"supplierId": "emdr-rmis-1",
+	"supplierDocId": "77700268-6023-4779-9902-000840bf1516",
+	"deltaMessageTime": "2025-11-24T08:48:14.000+00:00",
+	"patient": {
+		"surname1": "Красильникова",
+		"name": "Ольга",
+		"patrName": "Александровна",
+		"birthDate": "1980-09-05",
+		"snils": "33276225363",
+		"enp1": "1851982082633279",
+		"otherId1": {
+			"number": "8081342910",
+			"type": "1"
+		}
+	},
+	"representative": {
+		"surname": "",
+		"name": "",
+		"patrName": "",
+		"snils": ""
+	},
+	"docNumber": "0303202301",
+	"docSeries": "45"
+}</t>
+  </si>
+  <si>
+    <t>{
+	"emdrId": "224.16.25.09.000241022",
+	"kind": "224",
+	"organization": "1.2.643.5.1.13.13.12.2.16.1080",
+	"creationDateTime": "2026-06-20T08:25:38.000+00:00",
+	"patientSnils": "33276225363",
+	"regOkato": "92000000000",
+	"regionCode": "16",
+	"signer": [],
+	"processingStatus": "NEW",
+	"supplierId": "emdr-rmis-1",
+	"supplierDocId": "77700268-6023-4779-9902-000840bf1516",
+	"deltaMessageTime": "2025-11-24T08:48:14.000+00:00",
+	"patient": {
+		"surname1": "Красильникова",
+		"name1": "Ольга",
+		"patrName1": "Александровна",
+		"birthDate": "1980-09-05",
+		"snils": "33276225363",
+		"enp1": "1851982082633279",
+		"otherId": {
+			"number": "8081342910",
+			"type": "1"
+		}
+	},
+	"representative": {
+		"surname": "",
+		"name": "",
+		"patrName": "",
+		"snils": ""
+	},
+	"docNumber": "0303202301",
+	"docSeries": "45"
+}</t>
+  </si>
+  <si>
+    <t>{
+	"emdrId": "224.16.25.09.000241023",
+	"kind": "224",
+	"organization": "1.2.643.5.1.13.13.12.2.16.1080",
+	"creationDateTime": "2026-06-20T08:25:38.000+00:00",
+	"patientSnils": "33276225363",
+	"regOkato": "92000000000",
+	"regionCode": "16",
+	"signer": [],
+	"processingStatus": "NEW",
+	"supplierId": "emdr-rmis-1",
+	"supplierDocId": "77700268-6023-4779-9902-000840bf1516",
+	"deltaMessageTime": "2025-11-24T08:48:14.000+00:00",
+	"patient": {
+		"surname": "Красильникова",
+		"name": "Ольга",
+		"patrName1": "Александровна",
+		"birthDate1": "1980-09-05",
+		"snils": "33276225363",
+		"enp1": "1851982082633279",
+		"otherId": {
+			"number": "8081342910",
+			"type": "1"
+		}
+	},
+	"representative": {
+		"surname": "",
+		"name": "",
+		"patrName": "",
+		"snils": ""
+	},
+	"docNumber": "0303202301",
+	"docSeries": "45"
+}</t>
+  </si>
+  <si>
+    <t>{
+	"emdrId": "224.16.25.09.000241024",
+	"kind": "224",
+	"organization": "1.2.643.5.1.13.13.12.2.16.1080",
+	"creationDateTime": "2026-06-20T08:25:38.000+00:00",
+	"patientSnils": "33276225363",
+	"regOkato": "92000000000",
+	"regionCode": "16",
+	"signer": [],
+	"processingStatus": "NEW",
+	"supplierId": "emdr-rmis-1",
+	"supplierDocId": "77700268-6023-4779-9902-000840bf1516",
+	"deltaMessageTime": "2025-11-24T08:48:14.000+00:00",
+	"patient": {
+		"surname1": "Красильникова",
+		"name": "Ольга",
+		"patrName": "Александровна",
+		"birthDate1": "1980-09-05",
+		"snils": "33276225363",
+		"enp1": "1851982082633279",
+		"otherId": {
+			"number": "8081342910",
+			"type": "1"
+		}
+	},
+	"representative": {
+		"surname": "",
+		"name": "",
+		"patrName": "",
+		"snils": ""
+	},
+	"docNumber": "0303202301",
+	"docSeries": "45"
+}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -645,42 +1026,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1240,7 +1627,7 @@
       <c r="F13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="13" t="s">
         <v>25</v>
       </c>
       <c r="H13" s="3" t="s">
@@ -1293,23 +1680,243 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="13">
+        <v>10111000</v>
+      </c>
+      <c r="D16" s="13">
+        <v>10111000</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="13">
+        <v>10101100</v>
+      </c>
+      <c r="D17" s="13">
+        <v>10101100</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="13">
+        <v>10100011</v>
+      </c>
+      <c r="D18" s="13">
+        <v>10100011</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="13">
+        <v>10011011</v>
+      </c>
+      <c r="D19" s="13">
+        <v>10011011</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="13">
+        <v>10001111</v>
+      </c>
+      <c r="D20" s="13">
+        <v>10001111</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="13">
+        <v>10111000</v>
+      </c>
+      <c r="D21" s="13">
+        <v>10111000</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="13">
+        <v>10101100</v>
+      </c>
+      <c r="D22" s="13">
+        <v>10101100</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="13">
+        <v>10100011</v>
+      </c>
+      <c r="D23" s="13">
+        <v>10100011</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="13">
+        <v>10011011</v>
+      </c>
+      <c r="D24" s="13">
+        <v>10011011</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="13">
+        <v>10001111</v>
+      </c>
+      <c r="D25" s="13">
+        <v>10001111</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="33" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="34" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="35" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
